--- a/data/DOC-20251215-WA0003..xlsx
+++ b/data/DOC-20251215-WA0003..xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Descargas\Acciona Facility Services\Aplicaciones Webs\mi-app-qr\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3916FA21-02BF-458B-8497-7652A856C0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D9A484-3E07-42AF-B03F-689CD3784803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48168,7 +48168,7 @@
     </row>
     <row r="3153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3153">
-        <v>273473</v>
+        <v>243800</v>
       </c>
       <c r="B3153" t="s">
         <v>4384</v>
@@ -48179,7 +48179,7 @@
     </row>
     <row r="3154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3154">
-        <v>243800</v>
+        <v>273473</v>
       </c>
       <c r="B3154" t="s">
         <v>4386</v>
